--- a/10Mio_Initiative_Seeland_Biel.xlsx
+++ b/10Mio_Initiative_Seeland_Biel.xlsx
@@ -63,12 +63,12 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00375623"/>
+      <color rgb="00C00000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00C00000"/>
+      <color rgb="00375623"/>
       <sz val="9"/>
     </font>
     <font>
@@ -149,12 +149,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDEBD0"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -164,7 +159,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDEBD0"/>
       </patternFill>
     </fill>
   </fills>
@@ -233,66 +233,66 @@
     <xf numFmtId="3" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="5" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="10" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="5" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="5" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="5" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="7" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="10" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="8" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="10" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="8" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -672,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -776,13 +776,13 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>212484</v>
+        <v>223753</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>234762</v>
+        <v>247213</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>22278</v>
+        <v>23460</v>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>Bettlach</t>
+          <t>Biezwil</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
@@ -862,67 +862,71 @@
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Bezirk Lebern (SO)</t>
+          <t>Bezirk Bucheggberg (SO)</t>
         </is>
       </c>
       <c r="D10" s="17" t="n">
-        <v>4987</v>
+        <v>345</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>5510</v>
-      </c>
-      <c r="F10" s="17" t="n">
-        <v>523</v>
-      </c>
-      <c r="G10" s="18" t="n">
-        <v>0.00268614371859055</v>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>2062</t>
-        </is>
-      </c>
-      <c r="I10" s="19" t="inlineStr"/>
+        <v>381</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>36</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0.004455070708489384</v>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>⚠ Wenig Spielraum</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>Grenchen</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Schnottwil</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>Bezirk Lebern (SO)</t>
-        </is>
-      </c>
-      <c r="D11" s="22" t="n">
-        <v>18602</v>
-      </c>
-      <c r="E11" s="22" t="n">
-        <v>20552</v>
-      </c>
-      <c r="F11" s="22" t="n">
-        <v>1950</v>
-      </c>
-      <c r="G11" s="23" t="n">
-        <v>0.01218580696638227</v>
-      </c>
-      <c r="H11" s="24" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>Bezirk Bucheggberg (SO)</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="n">
+        <v>1176</v>
+      </c>
+      <c r="E11" s="24" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F11" s="25" t="n">
+        <v>123</v>
+      </c>
+      <c r="G11" s="26" t="n">
+        <v>0.01130105562802886</v>
+      </c>
+      <c r="H11" s="27" t="inlineStr">
         <is>
           <t>2033</t>
         </is>
       </c>
-      <c r="I11" s="25" t="inlineStr"/>
+      <c r="I11" s="28" t="inlineStr"/>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>Selzach</t>
+          <t>Bettlach</t>
         </is>
       </c>
       <c r="B12" s="16" t="inlineStr">
@@ -936,207 +940,207 @@
         </is>
       </c>
       <c r="D12" s="17" t="n">
-        <v>3690</v>
+        <v>4987</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>4077</v>
+        <v>5510</v>
       </c>
       <c r="F12" s="17" t="n">
-        <v>387</v>
-      </c>
-      <c r="G12" s="18" t="n">
-        <v>0.01368626989559374</v>
-      </c>
-      <c r="H12" s="24" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="I12" s="19" t="inlineStr"/>
+        <v>523</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>0.00268614371859055</v>
+      </c>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr"/>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>Aegerten</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>VK Biel/Bienne (BE)</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="n">
-        <v>2473</v>
-      </c>
-      <c r="E13" s="22" t="n">
-        <v>2732</v>
-      </c>
-      <c r="F13" s="26" t="n">
-        <v>259</v>
-      </c>
-      <c r="G13" s="27" t="n">
-        <v>0.02801423457045371</v>
-      </c>
-      <c r="H13" s="24" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="I13" s="25" t="inlineStr"/>
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>Grenchen</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>SO</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>Bezirk Lebern (SO)</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="n">
+        <v>18602</v>
+      </c>
+      <c r="E13" s="24" t="n">
+        <v>20552</v>
+      </c>
+      <c r="F13" s="24" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G13" s="26" t="n">
+        <v>0.01218580696638227</v>
+      </c>
+      <c r="H13" s="27" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="I13" s="28" t="inlineStr"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>Bellmund</t>
+          <t>Selzach</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>SO</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>VK Biel/Bienne (BE)</t>
+          <t>Bezirk Lebern (SO)</t>
         </is>
       </c>
       <c r="D14" s="17" t="n">
-        <v>1801</v>
+        <v>3690</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>1990</v>
-      </c>
-      <c r="F14" s="26" t="n">
-        <v>189</v>
-      </c>
-      <c r="G14" s="18" t="n">
-        <v>0.01203071569806013</v>
-      </c>
-      <c r="H14" s="24" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
-      </c>
-      <c r="I14" s="19" t="inlineStr"/>
+        <v>4077</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>387</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>0.01368626989559374</v>
+      </c>
+      <c r="H14" s="27" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr"/>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>Biel/Bienne</t>
-        </is>
-      </c>
-      <c r="B15" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C15" s="20" t="inlineStr">
-        <is>
-          <t>VK Biel/Bienne (BE)</t>
-        </is>
-      </c>
-      <c r="D15" s="22" t="n">
-        <v>56896</v>
-      </c>
-      <c r="E15" s="22" t="n">
-        <v>62861</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>5965</v>
-      </c>
-      <c r="G15" s="23" t="n">
-        <v>0.005859776958784035</v>
-      </c>
-      <c r="H15" s="28" t="inlineStr">
-        <is>
-          <t>2042</t>
-        </is>
-      </c>
-      <c r="I15" s="25" t="inlineStr"/>
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>Fräschels</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>Bezirk See / District du Lac (FR)</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="n">
+        <v>445</v>
+      </c>
+      <c r="E15" s="24" t="n">
+        <v>492</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>47</v>
+      </c>
+      <c r="G15" s="29" t="n">
+        <v>-0.002219846167627715</v>
+      </c>
+      <c r="H15" s="23" t="inlineStr">
+        <is>
+          <t>Kein Wachstum / schrumpfend</t>
+        </is>
+      </c>
+      <c r="I15" s="28" t="inlineStr">
+        <is>
+          <t>Schrumpfend – Limit wird nicht erreicht</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>Brügg</t>
+          <t>Kerzers (FR)</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>VK Biel/Bienne (BE)</t>
+          <t>Bezirk See / District du Lac (FR)</t>
         </is>
       </c>
       <c r="D16" s="17" t="n">
-        <v>4650</v>
+        <v>5466</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>5138</v>
+        <v>6039</v>
       </c>
       <c r="F16" s="17" t="n">
-        <v>488</v>
-      </c>
-      <c r="G16" s="18" t="n">
-        <v>0.009511471905427227</v>
-      </c>
-      <c r="H16" s="24" t="inlineStr">
-        <is>
-          <t>2035</t>
-        </is>
-      </c>
-      <c r="I16" s="19" t="inlineStr"/>
+        <v>573</v>
+      </c>
+      <c r="G16" s="19" t="n">
+        <v>0.0124888204705782</v>
+      </c>
+      <c r="H16" s="27" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr"/>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
-        <is>
-          <t>Bühl</t>
-        </is>
-      </c>
-      <c r="B17" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>VK Biel/Bienne (BE)</t>
-        </is>
-      </c>
-      <c r="D17" s="22" t="n">
-        <v>482</v>
-      </c>
-      <c r="E17" s="22" t="n">
-        <v>533</v>
-      </c>
-      <c r="F17" s="29" t="n">
-        <v>51</v>
-      </c>
-      <c r="G17" s="27" t="n">
-        <v>0.0165584928356779</v>
-      </c>
-      <c r="H17" s="24" t="inlineStr">
-        <is>
-          <t>2031</t>
-        </is>
-      </c>
-      <c r="I17" s="25" t="inlineStr">
-        <is>
-          <t>⚠ Wenig Spielraum</t>
-        </is>
-      </c>
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>Ried bei Kerzers (FR)</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>Bezirk See / District du Lac (FR)</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="n">
+        <v>1237</v>
+      </c>
+      <c r="E17" s="24" t="n">
+        <v>1367</v>
+      </c>
+      <c r="F17" s="25" t="n">
+        <v>130</v>
+      </c>
+      <c r="G17" s="26" t="n">
+        <v>0.01245319161034697</v>
+      </c>
+      <c r="H17" s="27" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="I17" s="28" t="inlineStr"/>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>Epsach</t>
+          <t>Aegerten</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
@@ -1150,67 +1154,63 @@
         </is>
       </c>
       <c r="D18" s="17" t="n">
-        <v>366</v>
+        <v>2473</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>404</v>
-      </c>
-      <c r="F18" s="29" t="n">
-        <v>38</v>
-      </c>
-      <c r="G18" s="18" t="n">
-        <v>0.01071455233024965</v>
-      </c>
-      <c r="H18" s="24" t="inlineStr">
-        <is>
-          <t>2034</t>
-        </is>
-      </c>
-      <c r="I18" s="19" t="inlineStr">
-        <is>
-          <t>⚠ Wenig Spielraum</t>
-        </is>
-      </c>
+        <v>2732</v>
+      </c>
+      <c r="F18" s="25" t="n">
+        <v>259</v>
+      </c>
+      <c r="G18" s="30" t="n">
+        <v>0.02801423457045371</v>
+      </c>
+      <c r="H18" s="27" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr"/>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>Evilard</t>
-        </is>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>Bellmund</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>VK Biel/Bienne (BE)</t>
         </is>
       </c>
-      <c r="D19" s="22" t="n">
-        <v>2657</v>
-      </c>
-      <c r="E19" s="22" t="n">
-        <v>2936</v>
-      </c>
-      <c r="F19" s="26" t="n">
-        <v>279</v>
-      </c>
-      <c r="G19" s="23" t="n">
-        <v>0.005347815729902949</v>
-      </c>
-      <c r="H19" s="28" t="inlineStr">
-        <is>
-          <t>2043</t>
-        </is>
-      </c>
-      <c r="I19" s="25" t="inlineStr"/>
+      <c r="D19" s="24" t="n">
+        <v>1801</v>
+      </c>
+      <c r="E19" s="24" t="n">
+        <v>1990</v>
+      </c>
+      <c r="F19" s="25" t="n">
+        <v>189</v>
+      </c>
+      <c r="G19" s="26" t="n">
+        <v>0.01203071569806013</v>
+      </c>
+      <c r="H19" s="27" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="I19" s="28" t="inlineStr"/>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>Hagneck</t>
+          <t>Biel/Bienne</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
@@ -1224,71 +1224,63 @@
         </is>
       </c>
       <c r="D20" s="17" t="n">
-        <v>436</v>
+        <v>56896</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>482</v>
-      </c>
-      <c r="F20" s="29" t="n">
-        <v>46</v>
-      </c>
-      <c r="G20" s="18" t="n">
-        <v>0.008403191865960391</v>
-      </c>
-      <c r="H20" s="28" t="inlineStr">
-        <is>
-          <t>2036</t>
-        </is>
-      </c>
-      <c r="I20" s="19" t="inlineStr">
-        <is>
-          <t>⚠ Wenig Spielraum</t>
-        </is>
-      </c>
+        <v>62861</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>5965</v>
+      </c>
+      <c r="G20" s="19" t="n">
+        <v>0.005859776958784035</v>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>2042</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr"/>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>Hermrigen</t>
-        </is>
-      </c>
-      <c r="B21" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>Brügg</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>VK Biel/Bienne (BE)</t>
         </is>
       </c>
-      <c r="D21" s="22" t="n">
-        <v>315</v>
-      </c>
-      <c r="E21" s="22" t="n">
-        <v>348</v>
-      </c>
-      <c r="F21" s="29" t="n">
-        <v>33</v>
-      </c>
-      <c r="G21" s="23" t="n">
-        <v>0.01367278323978893</v>
-      </c>
-      <c r="H21" s="24" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="I21" s="25" t="inlineStr">
-        <is>
-          <t>⚠ Wenig Spielraum</t>
-        </is>
-      </c>
+      <c r="D21" s="24" t="n">
+        <v>4650</v>
+      </c>
+      <c r="E21" s="24" t="n">
+        <v>5138</v>
+      </c>
+      <c r="F21" s="24" t="n">
+        <v>488</v>
+      </c>
+      <c r="G21" s="26" t="n">
+        <v>0.009511471905427227</v>
+      </c>
+      <c r="H21" s="27" t="inlineStr">
+        <is>
+          <t>2035</t>
+        </is>
+      </c>
+      <c r="I21" s="28" t="inlineStr"/>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>Ipsach</t>
+          <t>Bühl</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
@@ -1302,71 +1294,71 @@
         </is>
       </c>
       <c r="D22" s="17" t="n">
-        <v>3869</v>
+        <v>482</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>4275</v>
-      </c>
-      <c r="F22" s="17" t="n">
-        <v>406</v>
+        <v>533</v>
+      </c>
+      <c r="F22" s="18" t="n">
+        <v>51</v>
       </c>
       <c r="G22" s="30" t="n">
-        <v>-0.003697275351607021</v>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>Kein Wachstum / schrumpfend</t>
-        </is>
-      </c>
-      <c r="I22" s="19" t="inlineStr">
-        <is>
-          <t>Schrumpfend – Limit wird nicht erreicht</t>
+        <v>0.0165584928356779</v>
+      </c>
+      <c r="H22" s="27" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>⚠ Wenig Spielraum</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>Jens</t>
-        </is>
-      </c>
-      <c r="B23" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>Epsach</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>VK Biel/Bienne (BE)</t>
         </is>
       </c>
-      <c r="D23" s="22" t="n">
-        <v>660</v>
-      </c>
-      <c r="E23" s="22" t="n">
-        <v>729</v>
-      </c>
-      <c r="F23" s="29" t="n">
-        <v>69</v>
-      </c>
-      <c r="G23" s="31" t="n">
-        <v>-0.002980844748773914</v>
-      </c>
-      <c r="H23" s="21" t="inlineStr">
-        <is>
-          <t>Kein Wachstum / schrumpfend</t>
-        </is>
-      </c>
-      <c r="I23" s="25" t="inlineStr">
-        <is>
-          <t>Schrumpfend – Limit wird nicht erreicht</t>
+      <c r="D23" s="24" t="n">
+        <v>366</v>
+      </c>
+      <c r="E23" s="24" t="n">
+        <v>404</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <v>38</v>
+      </c>
+      <c r="G23" s="26" t="n">
+        <v>0.01071455233024965</v>
+      </c>
+      <c r="H23" s="27" t="inlineStr">
+        <is>
+          <t>2034</t>
+        </is>
+      </c>
+      <c r="I23" s="28" t="inlineStr">
+        <is>
+          <t>⚠ Wenig Spielraum</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>Lengnau (BE)</t>
+          <t>Evilard</t>
         </is>
       </c>
       <c r="B24" s="16" t="inlineStr">
@@ -1380,67 +1372,67 @@
         </is>
       </c>
       <c r="D24" s="17" t="n">
-        <v>5798</v>
+        <v>2657</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>6406</v>
-      </c>
-      <c r="F24" s="17" t="n">
-        <v>608</v>
-      </c>
-      <c r="G24" s="32" t="n">
-        <v>0.01805574725206949</v>
-      </c>
-      <c r="H24" s="24" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="I24" s="19" t="inlineStr"/>
+        <v>2936</v>
+      </c>
+      <c r="F24" s="25" t="n">
+        <v>279</v>
+      </c>
+      <c r="G24" s="19" t="n">
+        <v>0.005347815729902949</v>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr"/>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>Ligerz</t>
-        </is>
-      </c>
-      <c r="B25" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>Hagneck</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>VK Biel/Bienne (BE)</t>
         </is>
       </c>
-      <c r="D25" s="22" t="n">
-        <v>525</v>
-      </c>
-      <c r="E25" s="22" t="n">
-        <v>580</v>
-      </c>
-      <c r="F25" s="29" t="n">
-        <v>55</v>
-      </c>
-      <c r="G25" s="31" t="n">
-        <v>-0.003181701510506452</v>
-      </c>
-      <c r="H25" s="21" t="inlineStr">
-        <is>
-          <t>Kein Wachstum / schrumpfend</t>
-        </is>
-      </c>
-      <c r="I25" s="25" t="inlineStr">
-        <is>
-          <t>Schrumpfend – Limit wird nicht erreicht</t>
+      <c r="D25" s="24" t="n">
+        <v>436</v>
+      </c>
+      <c r="E25" s="24" t="n">
+        <v>482</v>
+      </c>
+      <c r="F25" s="18" t="n">
+        <v>46</v>
+      </c>
+      <c r="G25" s="26" t="n">
+        <v>0.008403191865960391</v>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>2036</t>
+        </is>
+      </c>
+      <c r="I25" s="28" t="inlineStr">
+        <is>
+          <t>⚠ Wenig Spielraum</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>Merzligen</t>
+          <t>Hermrigen</t>
         </is>
       </c>
       <c r="B26" s="16" t="inlineStr">
@@ -1454,71 +1446,71 @@
         </is>
       </c>
       <c r="D26" s="17" t="n">
-        <v>403</v>
+        <v>315</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>445</v>
-      </c>
-      <c r="F26" s="29" t="n">
-        <v>42</v>
-      </c>
-      <c r="G26" s="18" t="n">
-        <v>0.001753771130138082</v>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>2081</t>
-        </is>
-      </c>
-      <c r="I26" s="19" t="inlineStr">
+        <v>348</v>
+      </c>
+      <c r="F26" s="18" t="n">
+        <v>33</v>
+      </c>
+      <c r="G26" s="19" t="n">
+        <v>0.01367278323978893</v>
+      </c>
+      <c r="H26" s="27" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
         <is>
           <t>⚠ Wenig Spielraum</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
-        <is>
-          <t>Mörigen</t>
-        </is>
-      </c>
-      <c r="B27" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C27" s="20" t="inlineStr">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>Ipsach</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>VK Biel/Bienne (BE)</t>
         </is>
       </c>
-      <c r="D27" s="22" t="n">
-        <v>881</v>
-      </c>
-      <c r="E27" s="22" t="n">
-        <v>973</v>
-      </c>
-      <c r="F27" s="29" t="n">
-        <v>92</v>
-      </c>
-      <c r="G27" s="23" t="n">
-        <v>0.004062054502542711</v>
-      </c>
-      <c r="H27" s="28" t="inlineStr">
-        <is>
-          <t>2049</t>
-        </is>
-      </c>
-      <c r="I27" s="25" t="inlineStr">
-        <is>
-          <t>⚠ Wenig Spielraum</t>
+      <c r="D27" s="24" t="n">
+        <v>3869</v>
+      </c>
+      <c r="E27" s="24" t="n">
+        <v>4275</v>
+      </c>
+      <c r="F27" s="24" t="n">
+        <v>406</v>
+      </c>
+      <c r="G27" s="29" t="n">
+        <v>-0.003697275351607021</v>
+      </c>
+      <c r="H27" s="23" t="inlineStr">
+        <is>
+          <t>Kein Wachstum / schrumpfend</t>
+        </is>
+      </c>
+      <c r="I27" s="28" t="inlineStr">
+        <is>
+          <t>Schrumpfend – Limit wird nicht erreicht</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>Nidau</t>
+          <t>Jens</t>
         </is>
       </c>
       <c r="B28" s="16" t="inlineStr">
@@ -1532,63 +1524,67 @@
         </is>
       </c>
       <c r="D28" s="17" t="n">
-        <v>7053</v>
+        <v>660</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>7792</v>
-      </c>
-      <c r="F28" s="17" t="n">
-        <v>739</v>
-      </c>
-      <c r="G28" s="18" t="n">
-        <v>0.002282760552631657</v>
+        <v>729</v>
+      </c>
+      <c r="F28" s="18" t="n">
+        <v>69</v>
+      </c>
+      <c r="G28" s="31" t="n">
+        <v>-0.002980844748773914</v>
       </c>
       <c r="H28" s="16" t="inlineStr">
         <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="I28" s="19" t="inlineStr"/>
+          <t>Kein Wachstum / schrumpfend</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>Schrumpfend – Limit wird nicht erreicht</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>Orpund</t>
-        </is>
-      </c>
-      <c r="B29" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>Lengnau (BE)</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>VK Biel/Bienne (BE)</t>
         </is>
       </c>
-      <c r="D29" s="22" t="n">
-        <v>3373</v>
-      </c>
-      <c r="E29" s="22" t="n">
-        <v>3727</v>
-      </c>
-      <c r="F29" s="22" t="n">
-        <v>354</v>
-      </c>
-      <c r="G29" s="27" t="n">
-        <v>0.02484384009387486</v>
-      </c>
-      <c r="H29" s="24" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="I29" s="25" t="inlineStr"/>
+      <c r="D29" s="24" t="n">
+        <v>5798</v>
+      </c>
+      <c r="E29" s="24" t="n">
+        <v>6406</v>
+      </c>
+      <c r="F29" s="24" t="n">
+        <v>608</v>
+      </c>
+      <c r="G29" s="32" t="n">
+        <v>0.01805574725206949</v>
+      </c>
+      <c r="H29" s="27" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="I29" s="28" t="inlineStr"/>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ligerz</t>
         </is>
       </c>
       <c r="B30" s="16" t="inlineStr">
@@ -1602,63 +1598,71 @@
         </is>
       </c>
       <c r="D30" s="17" t="n">
-        <v>3904</v>
+        <v>525</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>4313</v>
-      </c>
-      <c r="F30" s="17" t="n">
-        <v>409</v>
-      </c>
-      <c r="G30" s="18" t="n">
-        <v>0.01454697831988572</v>
-      </c>
-      <c r="H30" s="24" t="inlineStr">
-        <is>
-          <t>2031</t>
-        </is>
-      </c>
-      <c r="I30" s="19" t="inlineStr"/>
+        <v>580</v>
+      </c>
+      <c r="F30" s="18" t="n">
+        <v>55</v>
+      </c>
+      <c r="G30" s="31" t="n">
+        <v>-0.003181701510506452</v>
+      </c>
+      <c r="H30" s="16" t="inlineStr">
+        <is>
+          <t>Kein Wachstum / schrumpfend</t>
+        </is>
+      </c>
+      <c r="I30" s="21" t="inlineStr">
+        <is>
+          <t>Schrumpfend – Limit wird nicht erreicht</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>Safnern</t>
-        </is>
-      </c>
-      <c r="B31" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="inlineStr">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>Merzligen</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>VK Biel/Bienne (BE)</t>
         </is>
       </c>
-      <c r="D31" s="22" t="n">
-        <v>2057</v>
-      </c>
-      <c r="E31" s="22" t="n">
-        <v>2273</v>
-      </c>
-      <c r="F31" s="26" t="n">
-        <v>216</v>
-      </c>
-      <c r="G31" s="23" t="n">
-        <v>0.007389362125590049</v>
-      </c>
-      <c r="H31" s="28" t="inlineStr">
-        <is>
-          <t>2038</t>
-        </is>
-      </c>
-      <c r="I31" s="25" t="inlineStr"/>
+      <c r="D31" s="24" t="n">
+        <v>403</v>
+      </c>
+      <c r="E31" s="24" t="n">
+        <v>445</v>
+      </c>
+      <c r="F31" s="18" t="n">
+        <v>42</v>
+      </c>
+      <c r="G31" s="26" t="n">
+        <v>0.001753771130138082</v>
+      </c>
+      <c r="H31" s="23" t="inlineStr">
+        <is>
+          <t>2081</t>
+        </is>
+      </c>
+      <c r="I31" s="28" t="inlineStr">
+        <is>
+          <t>⚠ Wenig Spielraum</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>Scheuren</t>
+          <t>Mörigen</t>
         </is>
       </c>
       <c r="B32" s="16" t="inlineStr">
@@ -1672,71 +1676,67 @@
         </is>
       </c>
       <c r="D32" s="17" t="n">
-        <v>535</v>
+        <v>881</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>591</v>
-      </c>
-      <c r="F32" s="29" t="n">
-        <v>56</v>
-      </c>
-      <c r="G32" s="18" t="n">
-        <v>0.01346975577472875</v>
-      </c>
-      <c r="H32" s="24" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="I32" s="19" t="inlineStr">
+        <v>973</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>92</v>
+      </c>
+      <c r="G32" s="19" t="n">
+        <v>0.004062054502542711</v>
+      </c>
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="inlineStr">
         <is>
           <t>⚠ Wenig Spielraum</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
-        <is>
-          <t>Schwadernau</t>
-        </is>
-      </c>
-      <c r="B33" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C33" s="20" t="inlineStr">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>Nidau</t>
+        </is>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
         <is>
           <t>VK Biel/Bienne (BE)</t>
         </is>
       </c>
-      <c r="D33" s="22" t="n">
-        <v>690</v>
-      </c>
-      <c r="E33" s="22" t="n">
-        <v>762</v>
-      </c>
-      <c r="F33" s="29" t="n">
-        <v>72</v>
-      </c>
-      <c r="G33" s="23" t="n">
-        <v>0.005372806647452988</v>
-      </c>
-      <c r="H33" s="28" t="inlineStr">
-        <is>
-          <t>2043</t>
-        </is>
-      </c>
-      <c r="I33" s="25" t="inlineStr">
-        <is>
-          <t>⚠ Wenig Spielraum</t>
-        </is>
-      </c>
+      <c r="D33" s="24" t="n">
+        <v>7053</v>
+      </c>
+      <c r="E33" s="24" t="n">
+        <v>7792</v>
+      </c>
+      <c r="F33" s="24" t="n">
+        <v>739</v>
+      </c>
+      <c r="G33" s="26" t="n">
+        <v>0.002282760552631657</v>
+      </c>
+      <c r="H33" s="23" t="inlineStr">
+        <is>
+          <t>2068</t>
+        </is>
+      </c>
+      <c r="I33" s="28" t="inlineStr"/>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t>Studen (BE)</t>
+          <t>Orpund</t>
         </is>
       </c>
       <c r="B34" s="16" t="inlineStr">
@@ -1750,67 +1750,63 @@
         </is>
       </c>
       <c r="D34" s="17" t="n">
-        <v>3537</v>
+        <v>3373</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>3908</v>
+        <v>3727</v>
       </c>
       <c r="F34" s="17" t="n">
-        <v>371</v>
-      </c>
-      <c r="G34" s="18" t="n">
-        <v>0.01304650051722978</v>
-      </c>
-      <c r="H34" s="24" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="I34" s="19" t="inlineStr"/>
+        <v>354</v>
+      </c>
+      <c r="G34" s="30" t="n">
+        <v>0.02484384009387486</v>
+      </c>
+      <c r="H34" s="27" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="I34" s="21" t="inlineStr"/>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="20" t="inlineStr">
-        <is>
-          <t>Sutz-Lattrigen</t>
-        </is>
-      </c>
-      <c r="B35" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C35" s="20" t="inlineStr">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>Port</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
         <is>
           <t>VK Biel/Bienne (BE)</t>
         </is>
       </c>
-      <c r="D35" s="22" t="n">
-        <v>1398</v>
-      </c>
-      <c r="E35" s="22" t="n">
-        <v>1545</v>
-      </c>
-      <c r="F35" s="26" t="n">
-        <v>147</v>
-      </c>
-      <c r="G35" s="31" t="n">
-        <v>-0.0008543409006646074</v>
-      </c>
-      <c r="H35" s="21" t="inlineStr">
-        <is>
-          <t>Kein Wachstum / schrumpfend</t>
-        </is>
-      </c>
-      <c r="I35" s="25" t="inlineStr">
-        <is>
-          <t>Schrumpfend – Limit wird nicht erreicht</t>
-        </is>
-      </c>
+      <c r="D35" s="24" t="n">
+        <v>3904</v>
+      </c>
+      <c r="E35" s="24" t="n">
+        <v>4313</v>
+      </c>
+      <c r="F35" s="24" t="n">
+        <v>409</v>
+      </c>
+      <c r="G35" s="26" t="n">
+        <v>0.01454697831988572</v>
+      </c>
+      <c r="H35" s="27" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="I35" s="28" t="inlineStr"/>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>Twann-Tüscherz</t>
+          <t>Safnern</t>
         </is>
       </c>
       <c r="B36" s="16" t="inlineStr">
@@ -1824,63 +1820,67 @@
         </is>
       </c>
       <c r="D36" s="17" t="n">
-        <v>1174</v>
+        <v>2057</v>
       </c>
       <c r="E36" s="17" t="n">
-        <v>1297</v>
-      </c>
-      <c r="F36" s="26" t="n">
-        <v>123</v>
-      </c>
-      <c r="G36" s="18" t="n">
-        <v>0.004809658662120242</v>
-      </c>
-      <c r="H36" s="28" t="inlineStr">
-        <is>
-          <t>2045</t>
-        </is>
-      </c>
-      <c r="I36" s="19" t="inlineStr"/>
+        <v>2273</v>
+      </c>
+      <c r="F36" s="25" t="n">
+        <v>216</v>
+      </c>
+      <c r="G36" s="19" t="n">
+        <v>0.007389362125590049</v>
+      </c>
+      <c r="H36" s="20" t="inlineStr">
+        <is>
+          <t>2038</t>
+        </is>
+      </c>
+      <c r="I36" s="21" t="inlineStr"/>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="20" t="inlineStr">
-        <is>
-          <t>Worben</t>
-        </is>
-      </c>
-      <c r="B37" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C37" s="20" t="inlineStr">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>Scheuren</t>
+        </is>
+      </c>
+      <c r="B37" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
         <is>
           <t>VK Biel/Bienne (BE)</t>
         </is>
       </c>
-      <c r="D37" s="22" t="n">
-        <v>2615</v>
-      </c>
-      <c r="E37" s="22" t="n">
-        <v>2889</v>
-      </c>
-      <c r="F37" s="26" t="n">
-        <v>274</v>
-      </c>
-      <c r="G37" s="23" t="n">
-        <v>0.01456228491036016</v>
-      </c>
-      <c r="H37" s="24" t="inlineStr">
-        <is>
-          <t>2031</t>
-        </is>
-      </c>
-      <c r="I37" s="25" t="inlineStr"/>
+      <c r="D37" s="24" t="n">
+        <v>535</v>
+      </c>
+      <c r="E37" s="24" t="n">
+        <v>591</v>
+      </c>
+      <c r="F37" s="18" t="n">
+        <v>56</v>
+      </c>
+      <c r="G37" s="26" t="n">
+        <v>0.01346975577472875</v>
+      </c>
+      <c r="H37" s="27" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="I37" s="28" t="inlineStr">
+        <is>
+          <t>⚠ Wenig Spielraum</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t>Aarberg</t>
+          <t>Schwadernau</t>
         </is>
       </c>
       <c r="B38" s="16" t="inlineStr">
@@ -1890,67 +1890,71 @@
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>VK Seeland (BE)</t>
+          <t>VK Biel/Bienne (BE)</t>
         </is>
       </c>
       <c r="D38" s="17" t="n">
-        <v>4620</v>
+        <v>690</v>
       </c>
       <c r="E38" s="17" t="n">
-        <v>5104</v>
-      </c>
-      <c r="F38" s="17" t="n">
-        <v>484</v>
-      </c>
-      <c r="G38" s="18" t="n">
-        <v>0.004389869637078103</v>
-      </c>
-      <c r="H38" s="28" t="inlineStr">
-        <is>
-          <t>2047</t>
-        </is>
-      </c>
-      <c r="I38" s="19" t="inlineStr"/>
+        <v>762</v>
+      </c>
+      <c r="F38" s="18" t="n">
+        <v>72</v>
+      </c>
+      <c r="G38" s="19" t="n">
+        <v>0.005372806647452988</v>
+      </c>
+      <c r="H38" s="20" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="I38" s="21" t="inlineStr">
+        <is>
+          <t>⚠ Wenig Spielraum</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="20" t="inlineStr">
-        <is>
-          <t>Arch</t>
-        </is>
-      </c>
-      <c r="B39" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C39" s="20" t="inlineStr">
-        <is>
-          <t>VK Seeland (BE)</t>
-        </is>
-      </c>
-      <c r="D39" s="22" t="n">
-        <v>1744</v>
-      </c>
-      <c r="E39" s="22" t="n">
-        <v>1927</v>
-      </c>
-      <c r="F39" s="26" t="n">
-        <v>183</v>
-      </c>
-      <c r="G39" s="23" t="n">
-        <v>0.01311122906368722</v>
-      </c>
-      <c r="H39" s="24" t="inlineStr">
+      <c r="A39" s="22" t="inlineStr">
+        <is>
+          <t>Studen (BE)</t>
+        </is>
+      </c>
+      <c r="B39" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C39" s="22" t="inlineStr">
+        <is>
+          <t>VK Biel/Bienne (BE)</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="n">
+        <v>3537</v>
+      </c>
+      <c r="E39" s="24" t="n">
+        <v>3908</v>
+      </c>
+      <c r="F39" s="24" t="n">
+        <v>371</v>
+      </c>
+      <c r="G39" s="26" t="n">
+        <v>0.01304650051722978</v>
+      </c>
+      <c r="H39" s="27" t="inlineStr">
         <is>
           <t>2032</t>
         </is>
       </c>
-      <c r="I39" s="25" t="inlineStr"/>
+      <c r="I39" s="28" t="inlineStr"/>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>Bargen (BE)</t>
+          <t>Sutz-Lattrigen</t>
         </is>
       </c>
       <c r="B40" s="16" t="inlineStr">
@@ -1960,71 +1964,71 @@
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>VK Seeland (BE)</t>
+          <t>VK Biel/Bienne (BE)</t>
         </is>
       </c>
       <c r="D40" s="17" t="n">
-        <v>1096</v>
+        <v>1398</v>
       </c>
       <c r="E40" s="17" t="n">
-        <v>1211</v>
-      </c>
-      <c r="F40" s="26" t="n">
-        <v>115</v>
-      </c>
-      <c r="G40" s="18" t="n">
-        <v>0.0110436517540069</v>
-      </c>
-      <c r="H40" s="24" t="inlineStr">
-        <is>
-          <t>2034</t>
-        </is>
-      </c>
-      <c r="I40" s="19" t="inlineStr"/>
+        <v>1545</v>
+      </c>
+      <c r="F40" s="25" t="n">
+        <v>147</v>
+      </c>
+      <c r="G40" s="31" t="n">
+        <v>-0.0008543409006646074</v>
+      </c>
+      <c r="H40" s="16" t="inlineStr">
+        <is>
+          <t>Kein Wachstum / schrumpfend</t>
+        </is>
+      </c>
+      <c r="I40" s="21" t="inlineStr">
+        <is>
+          <t>Schrumpfend – Limit wird nicht erreicht</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="20" t="inlineStr">
-        <is>
-          <t>Brüttelen</t>
-        </is>
-      </c>
-      <c r="B41" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C41" s="20" t="inlineStr">
-        <is>
-          <t>VK Seeland (BE)</t>
-        </is>
-      </c>
-      <c r="D41" s="22" t="n">
-        <v>641</v>
-      </c>
-      <c r="E41" s="22" t="n">
-        <v>708</v>
-      </c>
-      <c r="F41" s="29" t="n">
-        <v>67</v>
-      </c>
-      <c r="G41" s="23" t="n">
-        <v>0.01216419306853744</v>
-      </c>
-      <c r="H41" s="24" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
-      </c>
-      <c r="I41" s="25" t="inlineStr">
-        <is>
-          <t>⚠ Wenig Spielraum</t>
-        </is>
-      </c>
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>Twann-Tüscherz</t>
+        </is>
+      </c>
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C41" s="22" t="inlineStr">
+        <is>
+          <t>VK Biel/Bienne (BE)</t>
+        </is>
+      </c>
+      <c r="D41" s="24" t="n">
+        <v>1174</v>
+      </c>
+      <c r="E41" s="24" t="n">
+        <v>1297</v>
+      </c>
+      <c r="F41" s="25" t="n">
+        <v>123</v>
+      </c>
+      <c r="G41" s="26" t="n">
+        <v>0.004809658662120242</v>
+      </c>
+      <c r="H41" s="20" t="inlineStr">
+        <is>
+          <t>2045</t>
+        </is>
+      </c>
+      <c r="I41" s="28" t="inlineStr"/>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="15" t="inlineStr">
         <is>
-          <t>Büetigen</t>
+          <t>Worben</t>
         </is>
       </c>
       <c r="B42" s="16" t="inlineStr">
@@ -2034,71 +2038,67 @@
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
+          <t>VK Biel/Bienne (BE)</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="n">
+        <v>2615</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>2889</v>
+      </c>
+      <c r="F42" s="25" t="n">
+        <v>274</v>
+      </c>
+      <c r="G42" s="19" t="n">
+        <v>0.01456228491036016</v>
+      </c>
+      <c r="H42" s="27" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="I42" s="21" t="inlineStr"/>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="22" t="inlineStr">
+        <is>
+          <t>Aarberg</t>
+        </is>
+      </c>
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C43" s="22" t="inlineStr">
+        <is>
           <t>VK Seeland (BE)</t>
         </is>
       </c>
-      <c r="D42" s="17" t="n">
-        <v>916</v>
-      </c>
-      <c r="E42" s="17" t="n">
-        <v>1012</v>
-      </c>
-      <c r="F42" s="29" t="n">
-        <v>96</v>
-      </c>
-      <c r="G42" s="18" t="n">
-        <v>0.01125610664525967</v>
-      </c>
-      <c r="H42" s="24" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
-      </c>
-      <c r="I42" s="19" t="inlineStr">
-        <is>
-          <t>⚠ Wenig Spielraum</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="20" t="inlineStr">
-        <is>
-          <t>Büren an der Aare</t>
-        </is>
-      </c>
-      <c r="B43" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C43" s="20" t="inlineStr">
-        <is>
-          <t>VK Seeland (BE)</t>
-        </is>
-      </c>
-      <c r="D43" s="22" t="n">
-        <v>3806</v>
-      </c>
-      <c r="E43" s="22" t="n">
-        <v>4205</v>
-      </c>
-      <c r="F43" s="22" t="n">
-        <v>399</v>
-      </c>
-      <c r="G43" s="23" t="n">
-        <v>0.009985993643009117</v>
-      </c>
-      <c r="H43" s="24" t="inlineStr">
-        <is>
-          <t>2035</t>
-        </is>
-      </c>
-      <c r="I43" s="25" t="inlineStr"/>
+      <c r="D43" s="24" t="n">
+        <v>4620</v>
+      </c>
+      <c r="E43" s="24" t="n">
+        <v>5104</v>
+      </c>
+      <c r="F43" s="24" t="n">
+        <v>484</v>
+      </c>
+      <c r="G43" s="26" t="n">
+        <v>0.004389869637078103</v>
+      </c>
+      <c r="H43" s="20" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="I43" s="28" t="inlineStr"/>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" s="15" t="inlineStr">
         <is>
-          <t>Diessbach bei Büren</t>
+          <t>Arch</t>
         </is>
       </c>
       <c r="B44" s="16" t="inlineStr">
@@ -2112,63 +2112,63 @@
         </is>
       </c>
       <c r="D44" s="17" t="n">
-        <v>1052</v>
+        <v>1744</v>
       </c>
       <c r="E44" s="17" t="n">
-        <v>1162</v>
-      </c>
-      <c r="F44" s="26" t="n">
-        <v>110</v>
-      </c>
-      <c r="G44" s="18" t="n">
-        <v>0.008460579889415287</v>
-      </c>
-      <c r="H44" s="28" t="inlineStr">
-        <is>
-          <t>2036</t>
-        </is>
-      </c>
-      <c r="I44" s="19" t="inlineStr"/>
+        <v>1927</v>
+      </c>
+      <c r="F44" s="25" t="n">
+        <v>183</v>
+      </c>
+      <c r="G44" s="19" t="n">
+        <v>0.01311122906368722</v>
+      </c>
+      <c r="H44" s="27" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="I44" s="21" t="inlineStr"/>
     </row>
     <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="20" t="inlineStr">
-        <is>
-          <t>Dotzigen</t>
-        </is>
-      </c>
-      <c r="B45" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C45" s="20" t="inlineStr">
+      <c r="A45" s="22" t="inlineStr">
+        <is>
+          <t>Bargen (BE)</t>
+        </is>
+      </c>
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C45" s="22" t="inlineStr">
         <is>
           <t>VK Seeland (BE)</t>
         </is>
       </c>
-      <c r="D45" s="22" t="n">
-        <v>1580</v>
-      </c>
-      <c r="E45" s="22" t="n">
-        <v>1746</v>
-      </c>
-      <c r="F45" s="26" t="n">
-        <v>166</v>
-      </c>
-      <c r="G45" s="23" t="n">
-        <v>0.01044972437230451</v>
-      </c>
-      <c r="H45" s="24" t="inlineStr">
+      <c r="D45" s="24" t="n">
+        <v>1096</v>
+      </c>
+      <c r="E45" s="24" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F45" s="25" t="n">
+        <v>115</v>
+      </c>
+      <c r="G45" s="26" t="n">
+        <v>0.0110436517540069</v>
+      </c>
+      <c r="H45" s="27" t="inlineStr">
         <is>
           <t>2034</t>
         </is>
       </c>
-      <c r="I45" s="25" t="inlineStr"/>
+      <c r="I45" s="28" t="inlineStr"/>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" s="15" t="inlineStr">
         <is>
-          <t>Erlach</t>
+          <t>Brüttelen</t>
         </is>
       </c>
       <c r="B46" s="16" t="inlineStr">
@@ -2182,58 +2182,62 @@
         </is>
       </c>
       <c r="D46" s="17" t="n">
-        <v>1394</v>
+        <v>641</v>
       </c>
       <c r="E46" s="17" t="n">
-        <v>1540</v>
-      </c>
-      <c r="F46" s="26" t="n">
-        <v>146</v>
-      </c>
-      <c r="G46" s="18" t="n">
-        <v>0.003510154324699366</v>
-      </c>
-      <c r="H46" s="16" t="inlineStr">
-        <is>
-          <t>2053</t>
-        </is>
-      </c>
-      <c r="I46" s="19" t="inlineStr"/>
+        <v>708</v>
+      </c>
+      <c r="F46" s="18" t="n">
+        <v>67</v>
+      </c>
+      <c r="G46" s="19" t="n">
+        <v>0.01216419306853744</v>
+      </c>
+      <c r="H46" s="27" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="I46" s="21" t="inlineStr">
+        <is>
+          <t>⚠ Wenig Spielraum</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>Finsterhennen</t>
-        </is>
-      </c>
-      <c r="B47" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C47" s="20" t="inlineStr">
+      <c r="A47" s="22" t="inlineStr">
+        <is>
+          <t>Büetigen</t>
+        </is>
+      </c>
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C47" s="22" t="inlineStr">
         <is>
           <t>VK Seeland (BE)</t>
         </is>
       </c>
-      <c r="D47" s="22" t="n">
-        <v>570</v>
-      </c>
-      <c r="E47" s="22" t="n">
-        <v>630</v>
-      </c>
-      <c r="F47" s="29" t="n">
-        <v>60</v>
-      </c>
-      <c r="G47" s="23" t="n">
-        <v>0.007683374506004537</v>
-      </c>
-      <c r="H47" s="28" t="inlineStr">
-        <is>
-          <t>2038</t>
-        </is>
-      </c>
-      <c r="I47" s="25" t="inlineStr">
+      <c r="D47" s="24" t="n">
+        <v>916</v>
+      </c>
+      <c r="E47" s="24" t="n">
+        <v>1012</v>
+      </c>
+      <c r="F47" s="18" t="n">
+        <v>96</v>
+      </c>
+      <c r="G47" s="26" t="n">
+        <v>0.01125610664525967</v>
+      </c>
+      <c r="H47" s="27" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="I47" s="28" t="inlineStr">
         <is>
           <t>⚠ Wenig Spielraum</t>
         </is>
@@ -2242,7 +2246,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="15" t="inlineStr">
         <is>
-          <t>Gals</t>
+          <t>Büren an der Aare</t>
         </is>
       </c>
       <c r="B48" s="16" t="inlineStr">
@@ -2256,67 +2260,63 @@
         </is>
       </c>
       <c r="D48" s="17" t="n">
-        <v>849</v>
+        <v>3806</v>
       </c>
       <c r="E48" s="17" t="n">
-        <v>938</v>
-      </c>
-      <c r="F48" s="29" t="n">
-        <v>89</v>
-      </c>
-      <c r="G48" s="18" t="n">
-        <v>0.009814718652846777</v>
-      </c>
-      <c r="H48" s="24" t="inlineStr">
+        <v>4205</v>
+      </c>
+      <c r="F48" s="17" t="n">
+        <v>399</v>
+      </c>
+      <c r="G48" s="19" t="n">
+        <v>0.009985993643009117</v>
+      </c>
+      <c r="H48" s="27" t="inlineStr">
         <is>
           <t>2035</t>
         </is>
       </c>
-      <c r="I48" s="19" t="inlineStr">
-        <is>
-          <t>⚠ Wenig Spielraum</t>
-        </is>
-      </c>
+      <c r="I48" s="21" t="inlineStr"/>
     </row>
     <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="20" t="inlineStr">
-        <is>
-          <t>Gampelen</t>
-        </is>
-      </c>
-      <c r="B49" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C49" s="20" t="inlineStr">
+      <c r="A49" s="22" t="inlineStr">
+        <is>
+          <t>Diessbach bei Büren</t>
+        </is>
+      </c>
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C49" s="22" t="inlineStr">
         <is>
           <t>VK Seeland (BE)</t>
         </is>
       </c>
-      <c r="D49" s="22" t="n">
-        <v>1016</v>
-      </c>
-      <c r="E49" s="22" t="n">
-        <v>1123</v>
-      </c>
-      <c r="F49" s="26" t="n">
-        <v>107</v>
-      </c>
-      <c r="G49" s="27" t="n">
-        <v>0.01872068872388843</v>
-      </c>
-      <c r="H49" s="24" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="I49" s="25" t="inlineStr"/>
+      <c r="D49" s="24" t="n">
+        <v>1052</v>
+      </c>
+      <c r="E49" s="24" t="n">
+        <v>1162</v>
+      </c>
+      <c r="F49" s="25" t="n">
+        <v>110</v>
+      </c>
+      <c r="G49" s="26" t="n">
+        <v>0.008460579889415287</v>
+      </c>
+      <c r="H49" s="20" t="inlineStr">
+        <is>
+          <t>2036</t>
+        </is>
+      </c>
+      <c r="I49" s="28" t="inlineStr"/>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="15" t="inlineStr">
         <is>
-          <t>Grossaffoltern</t>
+          <t>Dotzigen</t>
         </is>
       </c>
       <c r="B50" s="16" t="inlineStr">
@@ -2330,63 +2330,63 @@
         </is>
       </c>
       <c r="D50" s="17" t="n">
-        <v>3070</v>
+        <v>1580</v>
       </c>
       <c r="E50" s="17" t="n">
-        <v>3392</v>
-      </c>
-      <c r="F50" s="17" t="n">
-        <v>322</v>
-      </c>
-      <c r="G50" s="18" t="n">
-        <v>0.004063291602344643</v>
-      </c>
-      <c r="H50" s="28" t="inlineStr">
-        <is>
-          <t>2049</t>
-        </is>
-      </c>
-      <c r="I50" s="19" t="inlineStr"/>
+        <v>1746</v>
+      </c>
+      <c r="F50" s="25" t="n">
+        <v>166</v>
+      </c>
+      <c r="G50" s="19" t="n">
+        <v>0.01044972437230451</v>
+      </c>
+      <c r="H50" s="27" t="inlineStr">
+        <is>
+          <t>2034</t>
+        </is>
+      </c>
+      <c r="I50" s="21" t="inlineStr"/>
     </row>
     <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="20" t="inlineStr">
-        <is>
-          <t>Ins</t>
-        </is>
-      </c>
-      <c r="B51" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C51" s="20" t="inlineStr">
+      <c r="A51" s="22" t="inlineStr">
+        <is>
+          <t>Erlach</t>
+        </is>
+      </c>
+      <c r="B51" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C51" s="22" t="inlineStr">
         <is>
           <t>VK Seeland (BE)</t>
         </is>
       </c>
-      <c r="D51" s="22" t="n">
-        <v>3777</v>
-      </c>
-      <c r="E51" s="22" t="n">
-        <v>4173</v>
-      </c>
-      <c r="F51" s="22" t="n">
-        <v>396</v>
-      </c>
-      <c r="G51" s="23" t="n">
-        <v>0.01039277980322173</v>
-      </c>
-      <c r="H51" s="24" t="inlineStr">
-        <is>
-          <t>2034</t>
-        </is>
-      </c>
-      <c r="I51" s="25" t="inlineStr"/>
+      <c r="D51" s="24" t="n">
+        <v>1394</v>
+      </c>
+      <c r="E51" s="24" t="n">
+        <v>1540</v>
+      </c>
+      <c r="F51" s="25" t="n">
+        <v>146</v>
+      </c>
+      <c r="G51" s="26" t="n">
+        <v>0.003510154324699366</v>
+      </c>
+      <c r="H51" s="23" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="I51" s="28" t="inlineStr"/>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" s="15" t="inlineStr">
         <is>
-          <t>Kallnach</t>
+          <t>Finsterhennen</t>
         </is>
       </c>
       <c r="B52" s="16" t="inlineStr">
@@ -2400,63 +2400,71 @@
         </is>
       </c>
       <c r="D52" s="17" t="n">
-        <v>2235</v>
+        <v>570</v>
       </c>
       <c r="E52" s="17" t="n">
-        <v>2469</v>
-      </c>
-      <c r="F52" s="26" t="n">
-        <v>234</v>
-      </c>
-      <c r="G52" s="18" t="n">
-        <v>0.01368267929555311</v>
-      </c>
-      <c r="H52" s="24" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="I52" s="19" t="inlineStr"/>
+        <v>630</v>
+      </c>
+      <c r="F52" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="G52" s="19" t="n">
+        <v>0.007683374506004537</v>
+      </c>
+      <c r="H52" s="20" t="inlineStr">
+        <is>
+          <t>2038</t>
+        </is>
+      </c>
+      <c r="I52" s="21" t="inlineStr">
+        <is>
+          <t>⚠ Wenig Spielraum</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="20" t="inlineStr">
-        <is>
-          <t>Kappelen</t>
-        </is>
-      </c>
-      <c r="B53" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C53" s="20" t="inlineStr">
+      <c r="A53" s="22" t="inlineStr">
+        <is>
+          <t>Gals</t>
+        </is>
+      </c>
+      <c r="B53" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C53" s="22" t="inlineStr">
         <is>
           <t>VK Seeland (BE)</t>
         </is>
       </c>
-      <c r="D53" s="22" t="n">
-        <v>1409</v>
-      </c>
-      <c r="E53" s="22" t="n">
-        <v>1557</v>
-      </c>
-      <c r="F53" s="26" t="n">
-        <v>148</v>
-      </c>
-      <c r="G53" s="23" t="n">
-        <v>0.005183816846277223</v>
-      </c>
-      <c r="H53" s="28" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="I53" s="25" t="inlineStr"/>
+      <c r="D53" s="24" t="n">
+        <v>849</v>
+      </c>
+      <c r="E53" s="24" t="n">
+        <v>938</v>
+      </c>
+      <c r="F53" s="18" t="n">
+        <v>89</v>
+      </c>
+      <c r="G53" s="26" t="n">
+        <v>0.009814718652846777</v>
+      </c>
+      <c r="H53" s="27" t="inlineStr">
+        <is>
+          <t>2035</t>
+        </is>
+      </c>
+      <c r="I53" s="28" t="inlineStr">
+        <is>
+          <t>⚠ Wenig Spielraum</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" s="15" t="inlineStr">
         <is>
-          <t>Leuzigen</t>
+          <t>Gampelen</t>
         </is>
       </c>
       <c r="B54" s="16" t="inlineStr">
@@ -2470,63 +2478,63 @@
         </is>
       </c>
       <c r="D54" s="17" t="n">
-        <v>1361</v>
+        <v>1016</v>
       </c>
       <c r="E54" s="17" t="n">
-        <v>1504</v>
-      </c>
-      <c r="F54" s="26" t="n">
-        <v>143</v>
-      </c>
-      <c r="G54" s="18" t="n">
-        <v>0.01000783258302906</v>
-      </c>
-      <c r="H54" s="24" t="inlineStr">
-        <is>
-          <t>2035</t>
-        </is>
-      </c>
-      <c r="I54" s="19" t="inlineStr"/>
+        <v>1123</v>
+      </c>
+      <c r="F54" s="25" t="n">
+        <v>107</v>
+      </c>
+      <c r="G54" s="30" t="n">
+        <v>0.01872068872388843</v>
+      </c>
+      <c r="H54" s="27" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="I54" s="21" t="inlineStr"/>
     </row>
     <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="20" t="inlineStr">
-        <is>
-          <t>Lyss</t>
-        </is>
-      </c>
-      <c r="B55" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C55" s="20" t="inlineStr">
+      <c r="A55" s="22" t="inlineStr">
+        <is>
+          <t>Grossaffoltern</t>
+        </is>
+      </c>
+      <c r="B55" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C55" s="22" t="inlineStr">
         <is>
           <t>VK Seeland (BE)</t>
         </is>
       </c>
-      <c r="D55" s="22" t="n">
-        <v>16558</v>
-      </c>
-      <c r="E55" s="22" t="n">
-        <v>18294</v>
-      </c>
-      <c r="F55" s="22" t="n">
-        <v>1736</v>
-      </c>
-      <c r="G55" s="27" t="n">
-        <v>0.01560300576611162</v>
-      </c>
-      <c r="H55" s="24" t="inlineStr">
-        <is>
-          <t>2031</t>
-        </is>
-      </c>
-      <c r="I55" s="25" t="inlineStr"/>
+      <c r="D55" s="24" t="n">
+        <v>3070</v>
+      </c>
+      <c r="E55" s="24" t="n">
+        <v>3392</v>
+      </c>
+      <c r="F55" s="24" t="n">
+        <v>322</v>
+      </c>
+      <c r="G55" s="26" t="n">
+        <v>0.004063291602344643</v>
+      </c>
+      <c r="H55" s="20" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="I55" s="28" t="inlineStr"/>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="15" t="inlineStr">
         <is>
-          <t>Lüscherz</t>
+          <t>Ins</t>
         </is>
       </c>
       <c r="B56" s="16" t="inlineStr">
@@ -2540,71 +2548,63 @@
         </is>
       </c>
       <c r="D56" s="17" t="n">
-        <v>572</v>
+        <v>3777</v>
       </c>
       <c r="E56" s="17" t="n">
-        <v>632</v>
-      </c>
-      <c r="F56" s="29" t="n">
-        <v>60</v>
-      </c>
-      <c r="G56" s="18" t="n">
-        <v>0.00803639058398864</v>
-      </c>
-      <c r="H56" s="28" t="inlineStr">
-        <is>
-          <t>2037</t>
-        </is>
-      </c>
-      <c r="I56" s="19" t="inlineStr">
-        <is>
-          <t>⚠ Wenig Spielraum</t>
-        </is>
-      </c>
+        <v>4173</v>
+      </c>
+      <c r="F56" s="17" t="n">
+        <v>396</v>
+      </c>
+      <c r="G56" s="19" t="n">
+        <v>0.01039277980322173</v>
+      </c>
+      <c r="H56" s="27" t="inlineStr">
+        <is>
+          <t>2034</t>
+        </is>
+      </c>
+      <c r="I56" s="21" t="inlineStr"/>
     </row>
     <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="20" t="inlineStr">
-        <is>
-          <t>Meienried</t>
-        </is>
-      </c>
-      <c r="B57" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C57" s="20" t="inlineStr">
+      <c r="A57" s="22" t="inlineStr">
+        <is>
+          <t>Kallnach</t>
+        </is>
+      </c>
+      <c r="B57" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C57" s="22" t="inlineStr">
         <is>
           <t>VK Seeland (BE)</t>
         </is>
       </c>
-      <c r="D57" s="22" t="n">
-        <v>57</v>
-      </c>
-      <c r="E57" s="22" t="n">
-        <v>63</v>
-      </c>
-      <c r="F57" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="G57" s="23" t="n">
-        <v>0.00542136482688238</v>
-      </c>
-      <c r="H57" s="28" t="inlineStr">
-        <is>
-          <t>2043</t>
-        </is>
-      </c>
-      <c r="I57" s="25" t="inlineStr">
-        <is>
-          <t>⚠ Wenig Spielraum</t>
-        </is>
-      </c>
+      <c r="D57" s="24" t="n">
+        <v>2235</v>
+      </c>
+      <c r="E57" s="24" t="n">
+        <v>2469</v>
+      </c>
+      <c r="F57" s="25" t="n">
+        <v>234</v>
+      </c>
+      <c r="G57" s="26" t="n">
+        <v>0.01368267929555311</v>
+      </c>
+      <c r="H57" s="27" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="I57" s="28" t="inlineStr"/>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="15" t="inlineStr">
         <is>
-          <t>Meinisberg</t>
+          <t>Kappelen</t>
         </is>
       </c>
       <c r="B58" s="16" t="inlineStr">
@@ -2618,63 +2618,63 @@
         </is>
       </c>
       <c r="D58" s="17" t="n">
-        <v>1453</v>
+        <v>1409</v>
       </c>
       <c r="E58" s="17" t="n">
-        <v>1605</v>
-      </c>
-      <c r="F58" s="26" t="n">
-        <v>152</v>
-      </c>
-      <c r="G58" s="18" t="n">
-        <v>0.00797859530159184</v>
-      </c>
-      <c r="H58" s="28" t="inlineStr">
-        <is>
-          <t>2037</t>
-        </is>
-      </c>
-      <c r="I58" s="19" t="inlineStr"/>
+        <v>1557</v>
+      </c>
+      <c r="F58" s="25" t="n">
+        <v>148</v>
+      </c>
+      <c r="G58" s="19" t="n">
+        <v>0.005183816846277223</v>
+      </c>
+      <c r="H58" s="20" t="inlineStr">
+        <is>
+          <t>2044</t>
+        </is>
+      </c>
+      <c r="I58" s="21" t="inlineStr"/>
     </row>
     <row r="59" ht="15" customHeight="1">
-      <c r="A59" s="20" t="inlineStr">
-        <is>
-          <t>Müntschemier</t>
-        </is>
-      </c>
-      <c r="B59" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C59" s="20" t="inlineStr">
+      <c r="A59" s="22" t="inlineStr">
+        <is>
+          <t>Leuzigen</t>
+        </is>
+      </c>
+      <c r="B59" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C59" s="22" t="inlineStr">
         <is>
           <t>VK Seeland (BE)</t>
         </is>
       </c>
-      <c r="D59" s="22" t="n">
-        <v>1652</v>
-      </c>
-      <c r="E59" s="22" t="n">
-        <v>1825</v>
-      </c>
-      <c r="F59" s="26" t="n">
-        <v>173</v>
-      </c>
-      <c r="G59" s="27" t="n">
-        <v>0.02354523222575544</v>
-      </c>
-      <c r="H59" s="24" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="I59" s="25" t="inlineStr"/>
+      <c r="D59" s="24" t="n">
+        <v>1361</v>
+      </c>
+      <c r="E59" s="24" t="n">
+        <v>1504</v>
+      </c>
+      <c r="F59" s="25" t="n">
+        <v>143</v>
+      </c>
+      <c r="G59" s="26" t="n">
+        <v>0.01000783258302906</v>
+      </c>
+      <c r="H59" s="27" t="inlineStr">
+        <is>
+          <t>2035</t>
+        </is>
+      </c>
+      <c r="I59" s="28" t="inlineStr"/>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="15" t="inlineStr">
         <is>
-          <t>Oberwil bei Büren</t>
+          <t>Lyss</t>
         </is>
       </c>
       <c r="B60" s="16" t="inlineStr">
@@ -2688,67 +2688,67 @@
         </is>
       </c>
       <c r="D60" s="17" t="n">
-        <v>904</v>
+        <v>16558</v>
       </c>
       <c r="E60" s="17" t="n">
-        <v>999</v>
-      </c>
-      <c r="F60" s="29" t="n">
-        <v>95</v>
-      </c>
-      <c r="G60" s="18" t="n">
-        <v>0.008820292147608377</v>
-      </c>
-      <c r="H60" s="28" t="inlineStr">
-        <is>
-          <t>2036</t>
-        </is>
-      </c>
-      <c r="I60" s="19" t="inlineStr">
+        <v>18294</v>
+      </c>
+      <c r="F60" s="17" t="n">
+        <v>1736</v>
+      </c>
+      <c r="G60" s="30" t="n">
+        <v>0.01560300576611162</v>
+      </c>
+      <c r="H60" s="27" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="I60" s="21" t="inlineStr"/>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" s="22" t="inlineStr">
+        <is>
+          <t>Lüscherz</t>
+        </is>
+      </c>
+      <c r="B61" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C61" s="22" t="inlineStr">
+        <is>
+          <t>VK Seeland (BE)</t>
+        </is>
+      </c>
+      <c r="D61" s="24" t="n">
+        <v>572</v>
+      </c>
+      <c r="E61" s="24" t="n">
+        <v>632</v>
+      </c>
+      <c r="F61" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="G61" s="26" t="n">
+        <v>0.00803639058398864</v>
+      </c>
+      <c r="H61" s="20" t="inlineStr">
+        <is>
+          <t>2037</t>
+        </is>
+      </c>
+      <c r="I61" s="28" t="inlineStr">
         <is>
           <t>⚠ Wenig Spielraum</t>
         </is>
       </c>
-    </row>
-    <row r="61" ht="15" customHeight="1">
-      <c r="A61" s="20" t="inlineStr">
-        <is>
-          <t>Pieterlen</t>
-        </is>
-      </c>
-      <c r="B61" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C61" s="20" t="inlineStr">
-        <is>
-          <t>VK Seeland (BE)</t>
-        </is>
-      </c>
-      <c r="D61" s="22" t="n">
-        <v>5216</v>
-      </c>
-      <c r="E61" s="22" t="n">
-        <v>5763</v>
-      </c>
-      <c r="F61" s="22" t="n">
-        <v>547</v>
-      </c>
-      <c r="G61" s="27" t="n">
-        <v>0.02764655235579094</v>
-      </c>
-      <c r="H61" s="24" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="I61" s="25" t="inlineStr"/>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="15" t="inlineStr">
         <is>
-          <t>Radelfingen</t>
+          <t>Meienried</t>
         </is>
       </c>
       <c r="B62" s="16" t="inlineStr">
@@ -2762,63 +2762,67 @@
         </is>
       </c>
       <c r="D62" s="17" t="n">
-        <v>1285</v>
+        <v>57</v>
       </c>
       <c r="E62" s="17" t="n">
-        <v>1420</v>
-      </c>
-      <c r="F62" s="26" t="n">
-        <v>135</v>
-      </c>
-      <c r="G62" s="18" t="n">
-        <v>0.005286712389867665</v>
-      </c>
-      <c r="H62" s="28" t="inlineStr">
+        <v>63</v>
+      </c>
+      <c r="F62" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="G62" s="19" t="n">
+        <v>0.00542136482688238</v>
+      </c>
+      <c r="H62" s="20" t="inlineStr">
         <is>
           <t>2043</t>
         </is>
       </c>
-      <c r="I62" s="19" t="inlineStr"/>
+      <c r="I62" s="21" t="inlineStr">
+        <is>
+          <t>⚠ Wenig Spielraum</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="15" customHeight="1">
-      <c r="A63" s="20" t="inlineStr">
-        <is>
-          <t>Rapperswil (BE)</t>
-        </is>
-      </c>
-      <c r="B63" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C63" s="20" t="inlineStr">
+      <c r="A63" s="22" t="inlineStr">
+        <is>
+          <t>Meikirch</t>
+        </is>
+      </c>
+      <c r="B63" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C63" s="22" t="inlineStr">
         <is>
           <t>VK Seeland (BE)</t>
         </is>
       </c>
-      <c r="D63" s="22" t="n">
-        <v>2705</v>
-      </c>
-      <c r="E63" s="22" t="n">
-        <v>2989</v>
-      </c>
-      <c r="F63" s="26" t="n">
-        <v>284</v>
-      </c>
-      <c r="G63" s="23" t="n">
-        <v>0.01119564457129729</v>
-      </c>
-      <c r="H63" s="24" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
-      </c>
-      <c r="I63" s="25" t="inlineStr"/>
+      <c r="D63" s="24" t="n">
+        <v>2600</v>
+      </c>
+      <c r="E63" s="24" t="n">
+        <v>2873</v>
+      </c>
+      <c r="F63" s="25" t="n">
+        <v>273</v>
+      </c>
+      <c r="G63" s="26" t="n">
+        <v>0.008162481836812008</v>
+      </c>
+      <c r="H63" s="20" t="inlineStr">
+        <is>
+          <t>2037</t>
+        </is>
+      </c>
+      <c r="I63" s="28" t="inlineStr"/>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" s="15" t="inlineStr">
         <is>
-          <t>Rüti bei Büren</t>
+          <t>Meinisberg</t>
         </is>
       </c>
       <c r="B64" s="16" t="inlineStr">
@@ -2832,67 +2836,63 @@
         </is>
       </c>
       <c r="D64" s="17" t="n">
-        <v>870</v>
+        <v>1453</v>
       </c>
       <c r="E64" s="17" t="n">
-        <v>961</v>
-      </c>
-      <c r="F64" s="29" t="n">
-        <v>91</v>
-      </c>
-      <c r="G64" s="18" t="n">
-        <v>0.005569151484128954</v>
-      </c>
-      <c r="H64" s="28" t="inlineStr">
-        <is>
-          <t>2042</t>
-        </is>
-      </c>
-      <c r="I64" s="19" t="inlineStr">
-        <is>
-          <t>⚠ Wenig Spielraum</t>
-        </is>
-      </c>
+        <v>1605</v>
+      </c>
+      <c r="F64" s="25" t="n">
+        <v>152</v>
+      </c>
+      <c r="G64" s="19" t="n">
+        <v>0.00797859530159184</v>
+      </c>
+      <c r="H64" s="20" t="inlineStr">
+        <is>
+          <t>2037</t>
+        </is>
+      </c>
+      <c r="I64" s="21" t="inlineStr"/>
     </row>
     <row r="65" ht="15" customHeight="1">
-      <c r="A65" s="20" t="inlineStr">
-        <is>
-          <t>Schüpfen</t>
-        </is>
-      </c>
-      <c r="B65" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C65" s="20" t="inlineStr">
+      <c r="A65" s="22" t="inlineStr">
+        <is>
+          <t>Müntschemier</t>
+        </is>
+      </c>
+      <c r="B65" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C65" s="22" t="inlineStr">
         <is>
           <t>VK Seeland (BE)</t>
         </is>
       </c>
-      <c r="D65" s="22" t="n">
-        <v>3784</v>
-      </c>
-      <c r="E65" s="22" t="n">
-        <v>4181</v>
-      </c>
-      <c r="F65" s="22" t="n">
-        <v>397</v>
-      </c>
-      <c r="G65" s="23" t="n">
-        <v>0.002790776888569102</v>
-      </c>
-      <c r="H65" s="21" t="inlineStr">
-        <is>
-          <t>2060</t>
-        </is>
-      </c>
-      <c r="I65" s="25" t="inlineStr"/>
+      <c r="D65" s="24" t="n">
+        <v>1652</v>
+      </c>
+      <c r="E65" s="24" t="n">
+        <v>1825</v>
+      </c>
+      <c r="F65" s="25" t="n">
+        <v>173</v>
+      </c>
+      <c r="G65" s="32" t="n">
+        <v>0.02354523222575544</v>
+      </c>
+      <c r="H65" s="27" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="I65" s="28" t="inlineStr"/>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" s="15" t="inlineStr">
         <is>
-          <t>Seedorf (BE)</t>
+          <t>Oberwil bei Büren</t>
         </is>
       </c>
       <c r="B66" s="16" t="inlineStr">
@@ -2906,67 +2906,67 @@
         </is>
       </c>
       <c r="D66" s="17" t="n">
-        <v>3235</v>
+        <v>904</v>
       </c>
       <c r="E66" s="17" t="n">
-        <v>3574</v>
-      </c>
-      <c r="F66" s="17" t="n">
-        <v>339</v>
-      </c>
-      <c r="G66" s="18" t="n">
-        <v>0.008651268041838023</v>
-      </c>
-      <c r="H66" s="28" t="inlineStr">
+        <v>999</v>
+      </c>
+      <c r="F66" s="18" t="n">
+        <v>95</v>
+      </c>
+      <c r="G66" s="19" t="n">
+        <v>0.008820292147608377</v>
+      </c>
+      <c r="H66" s="20" t="inlineStr">
         <is>
           <t>2036</t>
         </is>
       </c>
-      <c r="I66" s="19" t="inlineStr"/>
+      <c r="I66" s="21" t="inlineStr">
+        <is>
+          <t>⚠ Wenig Spielraum</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="15" customHeight="1">
-      <c r="A67" s="20" t="inlineStr">
-        <is>
-          <t>Siselen</t>
-        </is>
-      </c>
-      <c r="B67" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C67" s="20" t="inlineStr">
+      <c r="A67" s="22" t="inlineStr">
+        <is>
+          <t>Pieterlen</t>
+        </is>
+      </c>
+      <c r="B67" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C67" s="22" t="inlineStr">
         <is>
           <t>VK Seeland (BE)</t>
         </is>
       </c>
-      <c r="D67" s="22" t="n">
-        <v>633</v>
-      </c>
-      <c r="E67" s="22" t="n">
-        <v>699</v>
-      </c>
-      <c r="F67" s="29" t="n">
-        <v>66</v>
-      </c>
-      <c r="G67" s="23" t="n">
-        <v>0.008089488448755011</v>
-      </c>
-      <c r="H67" s="28" t="inlineStr">
-        <is>
-          <t>2037</t>
-        </is>
-      </c>
-      <c r="I67" s="25" t="inlineStr">
-        <is>
-          <t>⚠ Wenig Spielraum</t>
-        </is>
-      </c>
+      <c r="D67" s="24" t="n">
+        <v>5216</v>
+      </c>
+      <c r="E67" s="24" t="n">
+        <v>5763</v>
+      </c>
+      <c r="F67" s="24" t="n">
+        <v>547</v>
+      </c>
+      <c r="G67" s="32" t="n">
+        <v>0.02764655235579094</v>
+      </c>
+      <c r="H67" s="27" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="I67" s="28" t="inlineStr"/>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="15" t="inlineStr">
         <is>
-          <t>Treiten</t>
+          <t>Radelfingen</t>
         </is>
       </c>
       <c r="B68" s="16" t="inlineStr">
@@ -2980,71 +2980,63 @@
         </is>
       </c>
       <c r="D68" s="17" t="n">
-        <v>428</v>
+        <v>1285</v>
       </c>
       <c r="E68" s="17" t="n">
-        <v>473</v>
-      </c>
-      <c r="F68" s="29" t="n">
-        <v>45</v>
-      </c>
-      <c r="G68" s="18" t="n">
-        <v>0.0002339455963209502</v>
-      </c>
-      <c r="H68" s="16" t="inlineStr">
-        <is>
-          <t>2452</t>
-        </is>
-      </c>
-      <c r="I68" s="19" t="inlineStr">
-        <is>
-          <t>⚠ Wenig Spielraum</t>
-        </is>
-      </c>
+        <v>1420</v>
+      </c>
+      <c r="F68" s="25" t="n">
+        <v>135</v>
+      </c>
+      <c r="G68" s="19" t="n">
+        <v>0.005286712389867665</v>
+      </c>
+      <c r="H68" s="20" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="I68" s="21" t="inlineStr"/>
     </row>
     <row r="69" ht="15" customHeight="1">
-      <c r="A69" s="20" t="inlineStr">
-        <is>
-          <t>Tschugg</t>
-        </is>
-      </c>
-      <c r="B69" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C69" s="20" t="inlineStr">
+      <c r="A69" s="22" t="inlineStr">
+        <is>
+          <t>Rapperswil (BE)</t>
+        </is>
+      </c>
+      <c r="B69" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C69" s="22" t="inlineStr">
         <is>
           <t>VK Seeland (BE)</t>
         </is>
       </c>
-      <c r="D69" s="22" t="n">
-        <v>497</v>
-      </c>
-      <c r="E69" s="22" t="n">
-        <v>549</v>
-      </c>
-      <c r="F69" s="29" t="n">
-        <v>52</v>
-      </c>
-      <c r="G69" s="23" t="n">
-        <v>0.01225602694259753</v>
-      </c>
-      <c r="H69" s="24" t="inlineStr">
+      <c r="D69" s="24" t="n">
+        <v>2705</v>
+      </c>
+      <c r="E69" s="24" t="n">
+        <v>2989</v>
+      </c>
+      <c r="F69" s="25" t="n">
+        <v>284</v>
+      </c>
+      <c r="G69" s="26" t="n">
+        <v>0.01119564457129729</v>
+      </c>
+      <c r="H69" s="27" t="inlineStr">
         <is>
           <t>2033</t>
         </is>
       </c>
-      <c r="I69" s="25" t="inlineStr">
-        <is>
-          <t>⚠ Wenig Spielraum</t>
-        </is>
-      </c>
+      <c r="I69" s="28" t="inlineStr"/>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="15" t="inlineStr">
         <is>
-          <t>Täuffelen</t>
+          <t>Rüti bei Büren</t>
         </is>
       </c>
       <c r="B70" s="16" t="inlineStr">
@@ -3058,180 +3050,406 @@
         </is>
       </c>
       <c r="D70" s="17" t="n">
-        <v>3084</v>
+        <v>870</v>
       </c>
       <c r="E70" s="17" t="n">
-        <v>3407</v>
-      </c>
-      <c r="F70" s="17" t="n">
-        <v>323</v>
-      </c>
-      <c r="G70" s="18" t="n">
-        <v>0.01372479032589191</v>
-      </c>
-      <c r="H70" s="24" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="I70" s="19" t="inlineStr"/>
+        <v>961</v>
+      </c>
+      <c r="F70" s="18" t="n">
+        <v>91</v>
+      </c>
+      <c r="G70" s="19" t="n">
+        <v>0.005569151484128954</v>
+      </c>
+      <c r="H70" s="20" t="inlineStr">
+        <is>
+          <t>2042</t>
+        </is>
+      </c>
+      <c r="I70" s="21" t="inlineStr">
+        <is>
+          <t>⚠ Wenig Spielraum</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="15" customHeight="1">
-      <c r="A71" s="20" t="inlineStr">
-        <is>
-          <t>Vinelz</t>
-        </is>
-      </c>
-      <c r="B71" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C71" s="20" t="inlineStr">
+      <c r="A71" s="22" t="inlineStr">
+        <is>
+          <t>Schüpfen</t>
+        </is>
+      </c>
+      <c r="B71" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C71" s="22" t="inlineStr">
         <is>
           <t>VK Seeland (BE)</t>
         </is>
       </c>
-      <c r="D71" s="22" t="n">
-        <v>910</v>
-      </c>
-      <c r="E71" s="22" t="n">
-        <v>1005</v>
-      </c>
-      <c r="F71" s="29" t="n">
-        <v>95</v>
-      </c>
-      <c r="G71" s="23" t="n">
-        <v>0.006253786834570452</v>
-      </c>
-      <c r="H71" s="28" t="inlineStr">
-        <is>
-          <t>2040</t>
-        </is>
-      </c>
-      <c r="I71" s="25" t="inlineStr">
-        <is>
-          <t>⚠ Wenig Spielraum</t>
-        </is>
-      </c>
+      <c r="D71" s="24" t="n">
+        <v>3784</v>
+      </c>
+      <c r="E71" s="24" t="n">
+        <v>4181</v>
+      </c>
+      <c r="F71" s="24" t="n">
+        <v>397</v>
+      </c>
+      <c r="G71" s="26" t="n">
+        <v>0.002790776888569102</v>
+      </c>
+      <c r="H71" s="23" t="inlineStr">
+        <is>
+          <t>2060</t>
+        </is>
+      </c>
+      <c r="I71" s="28" t="inlineStr"/>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="15" t="inlineStr">
         <is>
+          <t>Seedorf (BE)</t>
+        </is>
+      </c>
+      <c r="B72" s="16" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C72" s="15" t="inlineStr">
+        <is>
+          <t>VK Seeland (BE)</t>
+        </is>
+      </c>
+      <c r="D72" s="17" t="n">
+        <v>3235</v>
+      </c>
+      <c r="E72" s="17" t="n">
+        <v>3574</v>
+      </c>
+      <c r="F72" s="17" t="n">
+        <v>339</v>
+      </c>
+      <c r="G72" s="19" t="n">
+        <v>0.008651268041838023</v>
+      </c>
+      <c r="H72" s="20" t="inlineStr">
+        <is>
+          <t>2036</t>
+        </is>
+      </c>
+      <c r="I72" s="21" t="inlineStr"/>
+    </row>
+    <row r="73" ht="15" customHeight="1">
+      <c r="A73" s="22" t="inlineStr">
+        <is>
+          <t>Siselen</t>
+        </is>
+      </c>
+      <c r="B73" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C73" s="22" t="inlineStr">
+        <is>
+          <t>VK Seeland (BE)</t>
+        </is>
+      </c>
+      <c r="D73" s="24" t="n">
+        <v>633</v>
+      </c>
+      <c r="E73" s="24" t="n">
+        <v>699</v>
+      </c>
+      <c r="F73" s="18" t="n">
+        <v>66</v>
+      </c>
+      <c r="G73" s="26" t="n">
+        <v>0.008089488448755011</v>
+      </c>
+      <c r="H73" s="20" t="inlineStr">
+        <is>
+          <t>2037</t>
+        </is>
+      </c>
+      <c r="I73" s="28" t="inlineStr">
+        <is>
+          <t>⚠ Wenig Spielraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="15" customHeight="1">
+      <c r="A74" s="15" t="inlineStr">
+        <is>
+          <t>Treiten</t>
+        </is>
+      </c>
+      <c r="B74" s="16" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C74" s="15" t="inlineStr">
+        <is>
+          <t>VK Seeland (BE)</t>
+        </is>
+      </c>
+      <c r="D74" s="17" t="n">
+        <v>428</v>
+      </c>
+      <c r="E74" s="17" t="n">
+        <v>473</v>
+      </c>
+      <c r="F74" s="18" t="n">
+        <v>45</v>
+      </c>
+      <c r="G74" s="19" t="n">
+        <v>0.0002339455963209502</v>
+      </c>
+      <c r="H74" s="16" t="inlineStr">
+        <is>
+          <t>2452</t>
+        </is>
+      </c>
+      <c r="I74" s="21" t="inlineStr">
+        <is>
+          <t>⚠ Wenig Spielraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="15" customHeight="1">
+      <c r="A75" s="22" t="inlineStr">
+        <is>
+          <t>Tschugg</t>
+        </is>
+      </c>
+      <c r="B75" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C75" s="22" t="inlineStr">
+        <is>
+          <t>VK Seeland (BE)</t>
+        </is>
+      </c>
+      <c r="D75" s="24" t="n">
+        <v>497</v>
+      </c>
+      <c r="E75" s="24" t="n">
+        <v>549</v>
+      </c>
+      <c r="F75" s="18" t="n">
+        <v>52</v>
+      </c>
+      <c r="G75" s="26" t="n">
+        <v>0.01225602694259753</v>
+      </c>
+      <c r="H75" s="27" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="I75" s="28" t="inlineStr">
+        <is>
+          <t>⚠ Wenig Spielraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="15" customHeight="1">
+      <c r="A76" s="15" t="inlineStr">
+        <is>
+          <t>Täuffelen</t>
+        </is>
+      </c>
+      <c r="B76" s="16" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C76" s="15" t="inlineStr">
+        <is>
+          <t>VK Seeland (BE)</t>
+        </is>
+      </c>
+      <c r="D76" s="17" t="n">
+        <v>3084</v>
+      </c>
+      <c r="E76" s="17" t="n">
+        <v>3407</v>
+      </c>
+      <c r="F76" s="17" t="n">
+        <v>323</v>
+      </c>
+      <c r="G76" s="19" t="n">
+        <v>0.01372479032589191</v>
+      </c>
+      <c r="H76" s="27" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="I76" s="21" t="inlineStr"/>
+    </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="A77" s="22" t="inlineStr">
+        <is>
+          <t>Vinelz</t>
+        </is>
+      </c>
+      <c r="B77" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C77" s="22" t="inlineStr">
+        <is>
+          <t>VK Seeland (BE)</t>
+        </is>
+      </c>
+      <c r="D77" s="24" t="n">
+        <v>910</v>
+      </c>
+      <c r="E77" s="24" t="n">
+        <v>1005</v>
+      </c>
+      <c r="F77" s="18" t="n">
+        <v>95</v>
+      </c>
+      <c r="G77" s="26" t="n">
+        <v>0.006253786834570452</v>
+      </c>
+      <c r="H77" s="20" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="I77" s="28" t="inlineStr">
+        <is>
+          <t>⚠ Wenig Spielraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="A78" s="15" t="inlineStr">
+        <is>
           <t>Walperswil</t>
         </is>
       </c>
-      <c r="B72" s="16" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C72" s="15" t="inlineStr">
+      <c r="B78" s="16" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="inlineStr">
         <is>
           <t>VK Seeland (BE)</t>
         </is>
       </c>
-      <c r="D72" s="17" t="n">
+      <c r="D78" s="17" t="n">
         <v>1045</v>
       </c>
-      <c r="E72" s="17" t="n">
+      <c r="E78" s="17" t="n">
         <v>1155</v>
       </c>
-      <c r="F72" s="26" t="n">
+      <c r="F78" s="25" t="n">
         <v>110</v>
       </c>
-      <c r="G72" s="18" t="n">
+      <c r="G78" s="19" t="n">
         <v>0.005828500977802076</v>
       </c>
-      <c r="H72" s="28" t="inlineStr">
+      <c r="H78" s="20" t="inlineStr">
         <is>
           <t>2042</t>
         </is>
       </c>
-      <c r="I72" s="19" t="inlineStr"/>
-    </row>
-    <row r="73" ht="15" customHeight="1">
-      <c r="A73" s="20" t="inlineStr">
+      <c r="I78" s="21" t="inlineStr"/>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="A79" s="22" t="inlineStr">
         <is>
           <t>Wengi</t>
         </is>
       </c>
-      <c r="B73" s="21" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C73" s="20" t="inlineStr">
+      <c r="B79" s="23" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C79" s="22" t="inlineStr">
         <is>
           <t>VK Seeland (BE)</t>
         </is>
       </c>
-      <c r="D73" s="22" t="n">
+      <c r="D79" s="24" t="n">
         <v>633</v>
       </c>
-      <c r="E73" s="22" t="n">
+      <c r="E79" s="24" t="n">
         <v>699</v>
       </c>
-      <c r="F73" s="29" t="n">
+      <c r="F79" s="18" t="n">
         <v>66</v>
       </c>
-      <c r="G73" s="23" t="n">
+      <c r="G79" s="26" t="n">
         <v>0.005704174016719632</v>
       </c>
-      <c r="H73" s="28" t="inlineStr">
+      <c r="H79" s="20" t="inlineStr">
         <is>
           <t>2042</t>
         </is>
       </c>
-      <c r="I73" s="25" t="inlineStr">
+      <c r="I79" s="28" t="inlineStr">
         <is>
           <t>⚠ Wenig Spielraum</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="33" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="33" t="inlineStr">
         <is>
           <t>Farbcode — Verfügbares Wachstum:</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="34" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  Viel Spielraum (≥2000 Pers.)</t>
         </is>
       </c>
-      <c r="D76" s="35" t="inlineStr">
+      <c r="D82" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">  Wenig Spielraum (&lt;300 Pers.)</t>
         </is>
       </c>
-      <c r="G76" s="36" t="inlineStr">
+      <c r="G82" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">  Sehr wenig (&lt;100 Pers.)</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="33" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="33" t="inlineStr">
         <is>
           <t>Farbcode — Limit erreicht:</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="35" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">  Sehr bald (bis 2035)</t>
         </is>
       </c>
-      <c r="D78" s="37" t="inlineStr">
+      <c r="D84" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">  Bald (2036–2050)</t>
         </is>
       </c>
-      <c r="G78" s="38" t="inlineStr">
+      <c r="G84" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  Längerfristig / kein Wachstum</t>
         </is>
@@ -3239,11 +3457,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A81:I81"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A75:I75"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A8:I8"/>
-    <mergeCell ref="A77:I77"/>
+    <mergeCell ref="A83:I83"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
